--- a/resources/report/60/95/stacrpstac710029.xlsx
+++ b/resources/report/60/95/stacrpstac710029.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871C538D-883F-4290-A17B-85802B5A32C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92847E0F-BFFE-43CF-B0C8-299D9F7CAC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AR History" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>Trans Date</t>
   </si>
@@ -167,6 +167,12 @@
   </si>
   <si>
     <t>REMARK2</t>
+  </si>
+  <si>
+    <t>Comercial Invoice No</t>
+  </si>
+  <si>
+    <t>C_INVOICE_NO</t>
   </si>
 </sst>
 </file>
@@ -877,7 +883,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -984,6 +990,21 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="28" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="33" borderId="8" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="33" borderId="1" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="33" borderId="21" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="33" borderId="22" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="33" borderId="5" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,12 +1017,6 @@
     <xf numFmtId="164" fontId="4" fillId="33" borderId="6" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="33" borderId="8" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="33" borderId="1" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="33" borderId="3" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1011,14 +1026,8 @@
     <xf numFmtId="43" fontId="4" fillId="33" borderId="3" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="33" borderId="21" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="33" borderId="22" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="43" fontId="4" fillId="33" borderId="3" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1340,38 +1349,39 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V13"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.6640625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="13.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.33203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="13.6640625" style="1" customWidth="1"/>
-    <col min="20" max="21" width="20.33203125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.6640625" style="1"/>
+    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" style="1" customWidth="1"/>
+    <col min="20" max="21" width="20.28515625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="19.85546875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1383,7 +1393,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="31"/>
       <c r="C3" s="3"/>
@@ -1395,14 +1405,14 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="32"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="28"/>
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
@@ -1411,52 +1421,55 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="6" spans="1:21" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:22" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="44" t="s">
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="J6" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="43" t="s">
+      <c r="K6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="36" t="s">
+      <c r="L6" s="44"/>
+      <c r="M6" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="39"/>
-      <c r="O6" s="36" t="s">
+      <c r="N6" s="44"/>
+      <c r="O6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="43" t="s">
+      <c r="P6" s="42"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="39"/>
-      <c r="T6" s="42" t="s">
+      <c r="S6" s="44"/>
+      <c r="T6" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="U6" s="42"/>
+      <c r="U6" s="45"/>
+      <c r="V6" s="48" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="7" spans="1:21" s="13" customFormat="1" ht="41.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
+    <row r="7" spans="1:22" s="13" customFormat="1" ht="41.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="37"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="33" t="s">
         <v>21</v>
       </c>
@@ -1475,8 +1488,8 @@
       <c r="H7" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="39"/>
       <c r="K7" s="27" t="s">
         <v>9</v>
       </c>
@@ -1510,8 +1523,9 @@
       <c r="U7" s="17" t="s">
         <v>14</v>
       </c>
+      <c r="V7" s="48"/>
     </row>
-    <row r="8" spans="1:21" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="18"/>
       <c r="C8" s="19"/>
@@ -1533,8 +1547,9 @@
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
       <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
     </row>
-    <row r="9" spans="1:21" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1598,11 +1613,14 @@
       <c r="U9" s="8" t="s">
         <v>47</v>
       </c>
+      <c r="V9" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U11" s="11"/>
     </row>
-    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="29" t="s">
         <v>16</v>
       </c>
@@ -1623,7 +1641,7 @@
       </c>
       <c r="U12" s="12"/>
     </row>
-    <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="30" t="s">
         <v>19</v>
       </c>
@@ -1646,7 +1664,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A8:U8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:V7"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="F4:G4"/>
@@ -1655,9 +1677,6 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="T6:U6"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.5" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" r:id="rId1"/>
